--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:22</t>
+    <t xml:space="preserve">2026-09-24 01:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -793,7 +793,7 @@
         <v>-0.46</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20">
@@ -807,7 +807,7 @@
         <v>-0.23</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="21">
@@ -821,7 +821,7 @@
         <v>-0.35</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="22">
@@ -835,7 +835,7 @@
         <v>-0.2</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="23">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_arica_y_parinacota.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:12</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_fonasa_a_2021_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
